--- a/htr-mapping-CDA/FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-mapping-CDA/FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:28:28+00:00</t>
+    <t>2025-05-14T12:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-mapping-CDA/FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-mapping-CDA/FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T12:14:19+00:00</t>
+    <t>2025-05-14T12:54:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
